--- a/StudentSummaryReport-Individual-Report-2026-07-23.xlsx
+++ b/StudentSummaryReport-Individual-Report-2026-07-23.xlsx
@@ -410,7 +410,7 @@
         <v>Generated On</v>
       </c>
       <c r="B2" t="str">
-        <v>7/23/2026, 9:50:01 PM</v>
+        <v>7/23/2026, 10:02:00 PM</v>
       </c>
     </row>
     <row r="3">

--- a/StudentSummaryReport-Individual-Report-2026-07-23.xlsx
+++ b/StudentSummaryReport-Individual-Report-2026-07-23.xlsx
@@ -410,7 +410,7 @@
         <v>Generated On</v>
       </c>
       <c r="B2" t="str">
-        <v>7/23/2026, 10:02:00 PM</v>
+        <v>7/23/2026, 11:07:21 PM</v>
       </c>
     </row>
     <row r="3">
